--- a/stacked_model/results/validation/validation_per_fold_comparison_summary.xlsx
+++ b/stacked_model/results/validation/validation_per_fold_comparison_summary.xlsx
@@ -495,31 +495,31 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3231519552120012</v>
+        <v>0.3294149756777449</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5410160482333128</v>
+        <v>0.3314636387638505</v>
       </c>
       <c r="E2" t="n">
-        <v>1.080510399095282</v>
+        <v>1.002293761515536</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02656592078777308</v>
+        <v>0.05280692761673472</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6074247424742797</v>
+        <v>0.6081524575329957</v>
       </c>
       <c r="H2" t="n">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="I2" t="n">
-        <v>938</v>
+        <v>870</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001602710325174783</v>
+        <v>0.01210474971112951</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2990734337055694</v>
+        <v>0.3286611054823361</v>
       </c>
     </row>
     <row r="3">
@@ -532,31 +532,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2597034070720468</v>
+        <v>0.2539360128045915</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3536171709839504</v>
+        <v>0.281210723695388</v>
       </c>
       <c r="E3" t="n">
-        <v>0.921417197727818</v>
+        <v>0.8348780146695426</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.004427798155813528</v>
+        <v>0.01566135308425642</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5022473202890034</v>
+        <v>0.4774503108886131</v>
       </c>
       <c r="H3" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="I3" t="n">
-        <v>903</v>
+        <v>895</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004837251764885586</v>
+        <v>0.006106674050635696</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2818521378941767</v>
+        <v>0.3041594201101381</v>
       </c>
     </row>
   </sheetData>
